--- a/Calendario_Mundial.xlsx
+++ b/Calendario_Mundial.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E01_Grupos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E02_16avos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E03_Octavos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E04_Cuartos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E05_Semis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E06_Final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="E01_Grupos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="E02_16avos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="E03_Octavos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="E04_Cuartos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="E05_Semis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="E06_Final" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,8 +492,6 @@
           <t>2026-06-11T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -524,8 +522,6 @@
           <t>2026-06-12T21:00:00-04:00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -556,8 +552,6 @@
           <t>2026-06-13T18:00:00-04:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -588,8 +582,6 @@
           <t>2026-06-14T00:00:00-04:00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -620,8 +612,6 @@
           <t>2026-06-14T16:00:00-04:00</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -652,8 +642,6 @@
           <t>2026-06-15T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -684,8 +672,6 @@
           <t>2026-06-16T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -716,8 +702,6 @@
           <t>2026-06-16T21:00:00-04:00</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -748,8 +732,6 @@
           <t>2026-06-17T16:00:00-04:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -780,8 +762,6 @@
           <t>2026-06-18T21:00:00-04:00</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -812,8 +792,6 @@
           <t>2026-06-19T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -844,8 +822,6 @@
           <t>2026-06-20T13:00:00-04:00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -876,8 +852,6 @@
           <t>2026-06-21T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -908,8 +882,6 @@
           <t>2026-06-22T13:00:00-04:00</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -940,8 +912,6 @@
           <t>2026-06-22T20:00:00-04:00</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -972,8 +942,6 @@
           <t>2026-06-24T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1004,8 +972,6 @@
           <t>2026-06-25T16:00:00-04:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1036,8 +1002,6 @@
           <t>2026-06-25T19:00:00-04:00</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1068,8 +1032,6 @@
           <t>2026-06-25T22:00:00-04:00</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1100,8 +1062,6 @@
           <t>2026-06-25T22:00:00-04:00</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1132,8 +1092,6 @@
           <t>2026-06-26T20:00:00-04:00</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1164,8 +1122,6 @@
           <t>2026-06-26T15:00:00-04:00</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1196,8 +1152,6 @@
           <t>2026-06-26T23:00:00-04:00</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1228,8 +1182,6 @@
           <t>2026-06-27T22:00:00-04:00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1260,8 +1212,6 @@
           <t>2026-06-27T19:30:00-04:00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1274,8 +1224,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1318,6 +1278,518 @@
           <t>notas</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sudáfrica</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-06-28T15:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Japón</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-29T13:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-29T16:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Holanda</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-29T21:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Costa de Marfil</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-30T13:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-30T17:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-30T21:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Congo</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-01T12:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bélgica</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-01T16:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bosnia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-01T20:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-02T15:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Croacia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-02T19:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-02T23:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Egipto</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-03T14:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cabo Verde</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-03T18:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-03T21:30:00-04:00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Calendario_Mundial.xlsx
+++ b/Calendario_Mundial.xlsx
@@ -2378,7 +2378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -2423,6 +2423,41 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-19T15:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>New York New Jersey Stadium, Estados Unidos</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
